--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_2404L.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_2404L.xlsx
@@ -1016,6 +1016,9 @@
           <t>2404-L-32-32</t>
         </is>
       </c>
+      <c r="D11" t="n">
+        <v>2.625</v>
+      </c>
       <c r="E11" t="n">
         <v>1.781</v>
       </c>
@@ -1034,12 +1037,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D@BORE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-CAD 2026-10-21: CHEX@HEX, D@BORE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 2404-L-32-32 (PARTcommunity / CADENAS, D@BORE=B1D, THDMAJ_B@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 2404-L-32-32 (PARTcommunity / CADENAS, CHEX@HEX=C, D@BORE=B1D, THDMAJ_B@DRIVE=B1THD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
